--- a/output/pdf_financials_xlsx/SPRQ.xlsx
+++ b/output/pdf_financials_xlsx/SPRQ.xlsx
@@ -653,22 +653,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.887281</v>
+        <v>0.125726</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.972178</v>
+        <v>0.084087</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>1.573918</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.22883</v>
+        <v>3.660503</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.135322</v>
+        <v>5.526433</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.586417</v>
+        <v>4.46832</v>
       </c>
     </row>
     <row r="11">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.983654</v>
+        <v>-0.222099</v>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
@@ -705,22 +705,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.00125</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002381</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.058652</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.058049</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.032802</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.011379</v>
       </c>
     </row>
     <row r="13">
@@ -1104,22 +1104,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.091988</v>
+        <v>-1.093238</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-7.806077</v>
+        <v>-7.808458</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.928314</v>
+        <v>-3.986966</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.76736</v>
+        <v>-4.825409</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-5.654344</v>
+        <v>-5.687146</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-4.907766</v>
+        <v>-4.919145</v>
       </c>
     </row>
     <row r="28">
@@ -1154,22 +1154,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.091988</v>
+        <v>-1.093238</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-7.806077</v>
+        <v>-7.808458</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.928314</v>
+        <v>-3.986966</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.76736</v>
+        <v>-4.825409</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.654344</v>
+        <v>-5.687146</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.907766</v>
+        <v>-4.919145</v>
       </c>
     </row>
     <row r="30">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-93412.14713430282</v>
+        <v>-93519.07613344739</v>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-2509.45382574641</v>
+        <v>-2540.009790710405</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-341.6800766225643</v>
+        <v>-343.6622322666804</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-208.8892842519423</v>
+        <v>-209.3736087216711</v>
       </c>
     </row>
     <row r="31">
@@ -3532,13 +3532,13 @@
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.014621</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.125628</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.203329</v>
       </c>
     </row>
     <row r="125">
@@ -3557,13 +3557,13 @@
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.014621</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.125628</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.203329</v>
       </c>
     </row>
     <row r="126">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
@@ -6688,7 +6688,11 @@
           <t>Lease payments 8</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -7354,7 +7358,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -9462,7 +9470,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -9640,7 +9648,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
@@ -13534,7 +13542,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E217" s="5" t="n">

--- a/output/pdf_financials_xlsx/SPRQ.xlsx
+++ b/output/pdf_financials_xlsx/SPRQ.xlsx
@@ -1129,22 +1129,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.022186</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.018112</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.032642</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.109804</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.215177</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.298201</v>
       </c>
     </row>
     <row r="29">
@@ -1154,22 +1154,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.093238</v>
+        <v>-1.071052</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-7.808458</v>
+        <v>-7.790346</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.986966</v>
+        <v>-3.954324</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.825409</v>
+        <v>-4.715605</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.687146</v>
+        <v>-5.471969</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.919145</v>
+        <v>-4.620944</v>
       </c>
     </row>
     <row r="30">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-93519.07613344739</v>
+        <v>-91621.21471343028</v>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-2540.009790710405</v>
+        <v>-2482.210910851897</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-343.6622322666804</v>
+        <v>-330.6595402041858</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-209.3736087216711</v>
+        <v>-196.6812771285973</v>
       </c>
     </row>
     <row r="31">
@@ -2935,10 +2935,10 @@
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.215177</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.298201</v>
       </c>
     </row>
     <row r="101">
@@ -6092,7 +6092,11 @@
           <t>Depreciation of property and equipment 6</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -9392,7 +9396,11 @@
           <t>Depreciation of property and equipment 6</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E125" s="5" t="n">
         <v>0.022186</v>
       </c>

--- a/output/pdf_financials_xlsx/SPRQ.xlsx
+++ b/output/pdf_financials_xlsx/SPRQ.xlsx
@@ -3198,22 +3198,22 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002414</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.036045</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.151115</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.294179</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.10168</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.09128600000000001</v>
       </c>
     </row>
     <row r="112">
@@ -3785,22 +3785,22 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002414</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.036045</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.151115</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.294179</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.10168</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.09128600000000001</v>
       </c>
     </row>
     <row r="135">
@@ -3810,22 +3810,22 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.332141</v>
+        <v>-0.334555</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.906145</v>
+        <v>-0.94219</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-4.559357</v>
+        <v>-4.710472</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-4.450895</v>
+        <v>-4.745074</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-5.201007</v>
+        <v>-5.302687</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-1.874822</v>
+        <v>-1.966108</v>
       </c>
     </row>
   </sheetData>
@@ -6568,7 +6568,11 @@
           <t>Acquisition of equipment 6</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
         <v>-0.002414</v>
       </c>
@@ -6738,7 +6742,11 @@
           <t>Proceeds from private placement 9</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
